--- a/Data/collapsed database manual cases/campeche_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/campeche_collapsed_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAE1CD1-530A-1642-9A2E-328D961B13D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBCDB3D-C169-ED4A-8BBE-E5DF1712D82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="266">
   <si>
     <t>uniqueid</t>
   </si>
@@ -1197,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -5336,6 +5336,26 @@
         <v>263</v>
       </c>
     </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>4012</v>
+      </c>
+      <c r="B95">
+        <v>2021</v>
+      </c>
+      <c r="E95" t="s">
+        <v>67</v>
+      </c>
+      <c r="F95" t="s">
+        <v>262</v>
+      </c>
+      <c r="H95" t="s">
+        <v>21</v>
+      </c>
+      <c r="I95" t="s">
+        <v>263</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S78" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
